--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121113224</v>
       </c>
       <c r="B2" t="n">
-        <v>41165</v>
+        <v>41168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,6 +804,148 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124081840</v>
+      </c>
+      <c r="B3" t="n">
+        <v>41292</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101261</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tunnvingemätare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Malacodea regelaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Tengström, 1869</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gillersklack, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>501737</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6641902</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Björn Larsson, Moa Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Björn Larsson, Moa Pettersson</t>
+          <t>Moa Pettersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Pettersson, Björn Larsson</t>
+          <t>Björn Larsson, Moa Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Björn Larsson, Moa Pettersson</t>
+          <t>Moa Pettersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>124081840</v>
       </c>
       <c r="B3" t="n">
-        <v>41574</v>
+        <v>41576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Pettersson, Björn Larsson</t>
+          <t>Björn Larsson, Moa Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>124081840</v>
       </c>
       <c r="B3" t="n">
-        <v>41576</v>
+        <v>41577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>124081840</v>
       </c>
       <c r="B3" t="n">
-        <v>41577</v>
+        <v>41580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>124081840</v>
       </c>
       <c r="B3" t="n">
-        <v>41580</v>
+        <v>41584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>124081840</v>
       </c>
       <c r="B3" t="n">
-        <v>41584</v>
+        <v>41585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>124081840</v>
       </c>
       <c r="B3" t="n">
-        <v>41585</v>
+        <v>41588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Björn Larsson, Moa Pettersson</t>
+          <t>Moa Pettersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 13233-2023 artfynd.xlsx
+++ b/artfynd/A 13233-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Pettersson, Björn Larsson</t>
+          <t>Björn Larsson, Moa Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
